--- a/center_sheet_C-1-2.xlsx
+++ b/center_sheet_C-1-2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dghy1\認知症ケア\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dghy1\center-method-sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8D8564-A084-49C7-B9ED-3CF7F3D6C94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B62E8A-3126-47B7-8CDC-F8E9473B5565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,7 +1036,7 @@
         <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6AB49388-702B-216A-2C59-F55D08C54DE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE5A1A73-5BC8-3A95-41CC-6D5CC8E9B984}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>

--- a/center_sheet_C-1-2.xlsx
+++ b/center_sheet_C-1-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dghy1\center-method-sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B62E8A-3126-47B7-8CDC-F8E9473B5565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059D7D48-63E1-49BE-8966-BA974834B7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,7 +1036,7 @@
         <xdr:cNvPr id="9" name="図 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE5A1A73-5BC8-3A95-41CC-6D5CC8E9B984}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE9036EE-D5DE-F40C-AB4B-6C71DF22E2C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1045,13 +1045,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:link="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>

--- a/center_sheet_C-1-2.xlsx
+++ b/center_sheet_C-1-2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dghy1\center-method-sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059D7D48-63E1-49BE-8966-BA974834B7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459800E1-B8CD-4F3A-882A-7A7C9E529B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1033,10 +1033,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
+        <xdr:cNvPr id="10" name="図 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EE9036EE-D5DE-F40C-AB4B-6C71DF22E2C7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFA8D5B5-EDED-5389-2266-65F0541CA3FA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
